--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487133_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487133_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.1028</v>
+        <v>7.6869</v>
       </c>
       <c r="E2" t="n">
-        <v>10.0951</v>
+        <v>8.8934</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-1.2065</v>
       </c>
       <c r="G2" t="n">
         <v>1.5571</v>
@@ -610,13 +610,13 @@
         <v>3.0881</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5289</v>
+        <v>1.1131</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0888</v>
+        <v>0.8871</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4402</v>
+        <v>0.226</v>
       </c>
       <c r="V2" t="n">
         <v>6.7538</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6824</v>
+        <v>2.3971</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9781</v>
+        <v>2.5761</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7043</v>
+        <v>-0.1791</v>
       </c>
       <c r="G3" t="n">
         <v>0.5736</v>
@@ -688,13 +688,13 @@
         <v>2.7021</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1041</v>
+        <v>1.8187</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3862</v>
+        <v>0.9842</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7179</v>
+        <v>0.8345</v>
       </c>
       <c r="V3" t="n">
         <v>2.1278</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. GONZALEZ RUIZ</t>
+          <t>I. JIMENEZ EL MERZOUG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4983</v>
+        <v>1.3854</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.055</v>
+        <v>1.628</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5533</v>
+        <v>-0.2426</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3033</v>
+        <v>0.8188</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0694</v>
+        <v>2.2419</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3727</v>
+        <v>-1.423</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1235</v>
+        <v>4.7489</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0828</v>
+        <v>4.0984</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0407</v>
+        <v>0.6505</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4268</v>
+        <v>-3.9301</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0134</v>
+        <v>-1.8566</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4134</v>
+        <v>-2.0735</v>
       </c>
       <c r="P4" t="n">
-        <v>0.386</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-4.8252</v>
       </c>
       <c r="R4" t="n">
-        <v>0.386</v>
+        <v>3.0881</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2406</v>
+        <v>0.1335</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1785</v>
+        <v>0.1904</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0621</v>
+        <v>-0.0569</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6562</v>
+        <v>2.1701</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X4" t="n">
         <v>0.6562</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. JIMENEZ EL MERZOUG</t>
+          <t>R. GONZALEZ RUIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2446</v>
+        <v>0.8057</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4263</v>
+        <v>0.1453</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6709000000000001</v>
+        <v>0.6603</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8188</v>
+        <v>-0.3033</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2419</v>
+        <v>0.0694</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.423</v>
+        <v>-0.3727</v>
       </c>
       <c r="J5" t="n">
-        <v>4.7489</v>
+        <v>0.1235</v>
       </c>
       <c r="K5" t="n">
-        <v>4.0984</v>
+        <v>0.0828</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6505</v>
+        <v>0.0407</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.9301</v>
+        <v>-0.4268</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8566</v>
+        <v>-0.0134</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.0735</v>
+        <v>-0.4134</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.7371</v>
+        <v>0.386</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.8252</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0881</v>
+        <v>0.386</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4965</v>
+        <v>0.0668</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0113</v>
+        <v>0.0218</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4852</v>
+        <v>0.0449</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1701</v>
+        <v>0.6562</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0.6562</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3473</v>
+        <v>0.5609</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8562</v>
+        <v>1.6573</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2034</v>
+        <v>-1.0964</v>
       </c>
       <c r="G6" t="n">
         <v>-3.8615</v>
@@ -922,13 +922,13 @@
         <v>2.3161</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6861</v>
+        <v>0.2221</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6544</v>
+        <v>0.1468</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0317</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>1.8842</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. SANCHEZ TURRION</t>
+          <t>M. HERRERO CRESPO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9257</v>
+        <v>-1.9304</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7045</v>
+        <v>1.5314</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2212</v>
+        <v>-3.4618</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.2275</v>
+        <v>-1.5002</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0536</v>
+        <v>-1.6416</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1738</v>
+        <v>0.1414</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2531</v>
+        <v>2.2695</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6262</v>
+        <v>-0.2124</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6269</v>
+        <v>2.482</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-3.7697</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4274</v>
+        <v>-1.4292</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-2.3406</v>
       </c>
       <c r="P7" t="n">
-        <v>0.386</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R7" t="n">
-        <v>0.386</v>
+        <v>2.8951</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2016</v>
+        <v>0.2261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5486</v>
+        <v>0.3573</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.347</v>
+        <v>-0.1312</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2859</v>
+        <v>-0.6562</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.7997</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2859</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. HERRERO CRESPO</t>
+          <t>L. SANCHEZ TURRION</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6581</v>
+        <v>-2.1458</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8304</v>
+        <v>-1.0049</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.4886</v>
+        <v>-1.1409</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5002</v>
+        <v>-2.2275</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6416</v>
+        <v>-1.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1414</v>
+        <v>-1.1738</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2695</v>
+        <v>-1.2531</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2124</v>
+        <v>-0.6262</v>
       </c>
       <c r="L8" t="n">
-        <v>2.482</v>
+        <v>-0.6269</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.7697</v>
+        <v>-0.9743000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4292</v>
+        <v>-0.4274</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.3406</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0.386</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8951</v>
+        <v>0.386</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5017</v>
+        <v>-0.0185</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3437</v>
+        <v>0.2482</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.158</v>
+        <v>-0.2667</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6562</v>
+        <v>-0.2859</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4559</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4244</v>
+        <v>-3.4511</v>
       </c>
       <c r="E9" t="n">
         <v>-2.6842</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7401</v>
+        <v>-0.7669</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0189</v>
@@ -1156,13 +1156,13 @@
         <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5017</v>
+        <v>0.4749</v>
       </c>
       <c r="T9" t="n">
         <v>0.1917</v>
       </c>
       <c r="U9" t="n">
-        <v>0.31</v>
+        <v>0.2832</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9421</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8682</v>
+        <v>-3.4934</v>
       </c>
       <c r="E10" t="n">
         <v>-1.2335</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6347</v>
+        <v>-2.2599</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8106</v>
@@ -1234,13 +1234,13 @@
         <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4785</v>
+        <v>-0.1038</v>
       </c>
       <c r="T10" t="n">
         <v>0.0727</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5513</v>
+        <v>-0.1765</v>
       </c>
       <c r="V10" t="n">
         <v>-1.228</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.815200000000001</v>
+        <v>1.8153</v>
       </c>
       <c r="E11" t="n">
         <v>11.5089</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.6937</v>
+        <v>-9.6938</v>
       </c>
       <c r="G11" t="n">
         <v>-7.7725</v>
@@ -1312,13 +1312,13 @@
         <v>16.4055</v>
       </c>
       <c r="S11" t="n">
-        <v>3.932900000000001</v>
+        <v>3.9329</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1001</v>
+        <v>3.1002</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8328000000000003</v>
+        <v>0.8326000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>10.4799</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.0776</v>
+        <v>6.2313</v>
       </c>
       <c r="E12" t="n">
-        <v>5.8616</v>
+        <v>5.9617</v>
       </c>
       <c r="F12" t="n">
-        <v>0.216</v>
+        <v>0.2695</v>
       </c>
       <c r="G12" t="n">
         <v>4.2242</v>
@@ -1390,13 +1390,13 @@
         <v>2.5091</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7958</v>
+        <v>-0.6421</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2247</v>
+        <v>-0.1246</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>1.1052</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9157</v>
+        <v>4.1566</v>
       </c>
       <c r="E13" t="n">
         <v>3.836</v>
       </c>
       <c r="F13" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.3206</v>
       </c>
       <c r="G13" t="n">
         <v>4.48</v>
@@ -1468,13 +1468,13 @@
         <v>3.8602</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8348</v>
+        <v>-0.5939</v>
       </c>
       <c r="T13" t="n">
         <v>-0.2247</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6101</v>
+        <v>-0.3692</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6945</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8276</v>
+        <v>0.9614</v>
       </c>
       <c r="E14" t="n">
         <v>4.1269</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.2993</v>
+        <v>-3.1655</v>
       </c>
       <c r="G14" t="n">
         <v>2.3886</v>
@@ -1546,13 +1546,13 @@
         <v>3.8602</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9353</v>
+        <v>-0.8015</v>
       </c>
       <c r="T14" t="n">
         <v>-0.2842</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6511</v>
+        <v>-0.5173</v>
       </c>
       <c r="V14" t="n">
         <v>-3.5208</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7985</v>
+        <v>0.7847</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0381</v>
+        <v>0.2383</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7605</v>
+        <v>0.5463</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0616</v>
@@ -1624,13 +1624,13 @@
         <v>1.158</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.275</v>
+        <v>-0.2889</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3569</v>
+        <v>-0.1566</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0819</v>
+        <v>-0.1322</v>
       </c>
       <c r="V15" t="n">
         <v>0.9421</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0939</v>
+        <v>-0.1262</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7956</v>
+        <v>0.4952</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7017</v>
+        <v>-0.6214</v>
       </c>
       <c r="G16" t="n">
         <v>0.6196</v>
@@ -1702,13 +1702,13 @@
         <v>0.772</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2162</v>
+        <v>-0.004</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4297</v>
+        <v>0.1292</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2135</v>
+        <v>-0.1332</v>
       </c>
       <c r="V16" t="n">
         <v>-1.5138</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>P. MOLINA MATA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5739</v>
+        <v>-1.5989</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5281</v>
+        <v>-1.4343</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0459</v>
+        <v>-0.1646</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3607</v>
+        <v>-3.0425</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.414</v>
+        <v>-1.7708</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7747000000000001</v>
+        <v>-1.2717</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4483</v>
+        <v>-1.0803</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1137</v>
+        <v>-0.502</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3345</v>
+        <v>-0.5783</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0875</v>
+        <v>-1.9621</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-1.2688</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5598</v>
+        <v>-0.6933</v>
       </c>
       <c r="P17" t="n">
-        <v>0.193</v>
+        <v>1.9301</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1231</v>
+        <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1229</v>
+        <v>-0.4865</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0462</v>
+        <v>-0.3539</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1692</v>
+        <v>-0.1325</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.2506</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.2506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ ORTEGA</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9281</v>
+        <v>-1.8486</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.194</v>
+        <v>-0.4279</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7341</v>
+        <v>-1.4206</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4178</v>
+        <v>0.3607</v>
       </c>
       <c r="H18" t="n">
-        <v>3.3078</v>
+        <v>-0.414</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.89</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8721</v>
+        <v>1.4483</v>
       </c>
       <c r="K18" t="n">
-        <v>3.9224</v>
+        <v>0.1137</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.0503</v>
+        <v>1.3345</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4543</v>
+        <v>-1.0875</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6146</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8397</v>
+        <v>-0.5598</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5441</v>
+        <v>0.193</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.8252</v>
+        <v>-1.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>3.2811</v>
+        <v>2.1231</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6524</v>
+        <v>-0.1517</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2842</v>
+        <v>0.0539</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3682</v>
+        <v>-0.2056</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1494</v>
+        <v>-2.2506</v>
       </c>
       <c r="W18" t="n">
-        <v>2.0433</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.1927</v>
+        <v>-2.2506</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. MOLINA MATA</t>
+          <t>A. FERNANDEZ ORTEGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1402</v>
+        <v>-2.1621</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7347</v>
+        <v>-0.2941</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4055</v>
+        <v>-1.8679</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.0425</v>
+        <v>1.4178</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7708</v>
+        <v>3.3078</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2717</v>
+        <v>-1.89</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0803</v>
+        <v>2.8721</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.502</v>
+        <v>3.9224</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5783</v>
+        <v>-1.0503</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9621</v>
+        <v>-1.4543</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2688</v>
+        <v>-0.6146</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6933</v>
+        <v>-0.8397</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9301</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-4.8252</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9301</v>
+        <v>3.2811</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0278</v>
+        <v>-0.8864</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6544</v>
+        <v>-0.3843</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3735</v>
+        <v>-0.5021</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.1494</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.0433</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-3.1927</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. LOPEZ BRETON</t>
+          <t>G. RUIZ ALCALA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5541</v>
+        <v>-2.513</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4552</v>
+        <v>-0.9006</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0988</v>
+        <v>-1.6124</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6096</v>
+        <v>-1.4058</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9481000000000001</v>
+        <v>0.2743</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3385</v>
+        <v>-1.6801</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3181</v>
+        <v>-0.1981</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3002</v>
+        <v>0.3881</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6183999999999999</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9277</v>
+        <v>-1.2076</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6478</v>
+        <v>-0.1137</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2799</v>
+        <v>-1.0939</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5441</v>
+        <v>0.579</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.386</v>
+        <v>0.579</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8276</v>
+        <v>-0.4161</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1567</v>
+        <v>-0.0462</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3292</v>
+        <v>-0.3698</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.228</v>
+        <v>-1.2702</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.228</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. RUIZ ALCALA</t>
+          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5934</v>
+        <v>-2.5524</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9006</v>
+        <v>-0.7512</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6927</v>
+        <v>-1.8012</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4058</v>
+        <v>-0.5989</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2743</v>
+        <v>-0.4347</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6801</v>
+        <v>-0.1642</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1981</v>
+        <v>-0.1522</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3881</v>
+        <v>-0.2743</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5862000000000001</v>
+        <v>0.1221</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2076</v>
+        <v>-0.4467</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1137</v>
+        <v>-0.1604</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0939</v>
+        <v>-0.2863</v>
       </c>
       <c r="P21" t="n">
-        <v>0.579</v>
+        <v>-1.158</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4964</v>
+        <v>0.1044</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0462</v>
+        <v>0.1031</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4501</v>
+        <v>0.0013</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2702</v>
+        <v>-0.8999</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6562</v>
+        <v>1.228</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.614</v>
+        <v>-2.1278</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
+          <t>A. LOPEZ BRETON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7388</v>
+        <v>-3.148</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1518</v>
+        <v>-1.1562</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.587</v>
+        <v>-1.9918</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5989</v>
+        <v>-0.6096</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4347</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1642</v>
+        <v>0.3385</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1522</v>
+        <v>0.3181</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2743</v>
+        <v>-0.3002</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1221</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4467</v>
+        <v>-0.9277</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1604</v>
+        <v>-0.6478</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2863</v>
+        <v>-0.2799</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.158</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>0.772</v>
+        <v>0.386</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.082</v>
+        <v>0.2337</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2974</v>
+        <v>0.4558</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2155</v>
+        <v>-0.2221</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8999</v>
+        <v>-1.228</v>
       </c>
       <c r="W22" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1278</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.815199999999997</v>
+        <v>-1.8152</v>
       </c>
       <c r="E23" t="n">
         <v>9.6938</v>
       </c>
       <c r="F23" t="n">
-        <v>-11.5088</v>
+        <v>-11.509</v>
       </c>
       <c r="G23" t="n">
         <v>7.772500000000001</v>
@@ -2248,13 +2248,13 @@
         <v>21.2308</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.9328</v>
+        <v>-3.933</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8324999999999999</v>
+        <v>-0.8325</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.1002</v>
+        <v>-3.1003</v>
       </c>
       <c r="V23" t="n">
         <v>-10.4799</v>
